--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I705"/>
+  <dimension ref="A1:I709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23701,6 +23701,138 @@
         <v>309.7</v>
       </c>
       <c r="I705" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>429.72</v>
+      </c>
+      <c r="C706" t="n">
+        <v>320.75</v>
+      </c>
+      <c r="D706" t="n">
+        <v>334.1</v>
+      </c>
+      <c r="E706" t="n">
+        <v>301.29</v>
+      </c>
+      <c r="F706" t="n">
+        <v>308.79</v>
+      </c>
+      <c r="G706" t="n">
+        <v>306.93</v>
+      </c>
+      <c r="H706" t="n">
+        <v>308.48</v>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>419.43</v>
+      </c>
+      <c r="C707" t="n">
+        <v>320.51</v>
+      </c>
+      <c r="D707" t="n">
+        <v>334.79</v>
+      </c>
+      <c r="E707" t="n">
+        <v>302.04</v>
+      </c>
+      <c r="F707" t="n">
+        <v>308.4</v>
+      </c>
+      <c r="G707" t="n">
+        <v>306.42</v>
+      </c>
+      <c r="H707" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>415.37</v>
+      </c>
+      <c r="C708" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="D708" t="n">
+        <v>335.54</v>
+      </c>
+      <c r="E708" t="n">
+        <v>301.98</v>
+      </c>
+      <c r="F708" t="n">
+        <v>308.57</v>
+      </c>
+      <c r="G708" t="n">
+        <v>306.75</v>
+      </c>
+      <c r="H708" t="n">
+        <v>309.28</v>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>406.39</v>
+      </c>
+      <c r="C709" t="n">
+        <v>320.11</v>
+      </c>
+      <c r="D709" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="E709" t="n">
+        <v>302.06</v>
+      </c>
+      <c r="F709" t="n">
+        <v>308.26</v>
+      </c>
+      <c r="G709" t="n">
+        <v>306.48</v>
+      </c>
+      <c r="H709" t="n">
+        <v>309.27</v>
+      </c>
+      <c r="I709" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23717,7 +23849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31110,6 +31242,46 @@
       </c>
       <c r="B739" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -31278,28 +31450,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.345070621059999</v>
+        <v>1.308673728169489</v>
       </c>
       <c r="J2" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K2" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0358826327061007</v>
+        <v>0.03439997537469419</v>
       </c>
       <c r="M2" t="n">
-        <v>44.62543885095626</v>
+        <v>44.56350699502457</v>
       </c>
       <c r="N2" t="n">
-        <v>2690.204942937203</v>
+        <v>2680.861501004395</v>
       </c>
       <c r="O2" t="n">
-        <v>51.86718560840951</v>
+        <v>51.7770364254695</v>
       </c>
       <c r="P2" t="n">
-        <v>413.0107558684659</v>
+        <v>413.3967981320494</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31360,28 +31532,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00180183134526892</v>
+        <v>-0.0005133666112925664</v>
       </c>
       <c r="J3" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K3" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L3" t="n">
-        <v>1.817434078443814e-05</v>
+        <v>1.491614437743038e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.372176570994558</v>
+        <v>2.371216937940384</v>
       </c>
       <c r="N3" t="n">
-        <v>9.978121021361268</v>
+        <v>9.944643046290736</v>
       </c>
       <c r="O3" t="n">
-        <v>3.158816395639555</v>
+        <v>3.153512810548062</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4732623244068</v>
+        <v>322.4976514834296</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31442,28 +31614,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2730195054632865</v>
+        <v>0.2715234237406272</v>
       </c>
       <c r="J4" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K4" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2987130510502369</v>
+        <v>0.2989510713889451</v>
       </c>
       <c r="M4" t="n">
-        <v>2.200838013507976</v>
+        <v>2.195921261900983</v>
       </c>
       <c r="N4" t="n">
-        <v>9.774981902586108</v>
+        <v>9.730922299648537</v>
       </c>
       <c r="O4" t="n">
-        <v>3.126496745974015</v>
+        <v>3.119442626439624</v>
       </c>
       <c r="P4" t="n">
-        <v>328.9059376769032</v>
+        <v>328.921690563431</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31524,28 +31696,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00277456559430175</v>
+        <v>-0.003105192054354811</v>
       </c>
       <c r="J5" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K5" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L5" t="n">
-        <v>2.323506082457794e-05</v>
+        <v>2.925873094261622e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.230558171521002</v>
+        <v>3.240170652612703</v>
       </c>
       <c r="N5" t="n">
-        <v>18.50645093600574</v>
+        <v>18.54812127068985</v>
       </c>
       <c r="O5" t="n">
-        <v>4.301912474238143</v>
+        <v>4.306752984638178</v>
       </c>
       <c r="P5" t="n">
-        <v>306.8951345859467</v>
+        <v>306.9570650473874</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31602,28 +31774,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03423294011216223</v>
+        <v>0.02593271452586272</v>
       </c>
       <c r="J6" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K6" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002846148689890415</v>
+        <v>0.001636293094809615</v>
       </c>
       <c r="M6" t="n">
-        <v>3.472297559736556</v>
+        <v>3.49149865225806</v>
       </c>
       <c r="N6" t="n">
-        <v>22.93401215833785</v>
+        <v>23.0948333298483</v>
       </c>
       <c r="O6" t="n">
-        <v>4.788946873618234</v>
+        <v>4.80570841082231</v>
       </c>
       <c r="P6" t="n">
-        <v>314.8188052394682</v>
+        <v>314.9062360902557</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31680,28 +31852,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02876021481425685</v>
+        <v>0.01943816097238156</v>
       </c>
       <c r="J7" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K7" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002325601596908977</v>
+        <v>0.001058231597975023</v>
       </c>
       <c r="M7" t="n">
-        <v>3.204200828744879</v>
+        <v>3.231817356465426</v>
       </c>
       <c r="N7" t="n">
-        <v>19.82096586738257</v>
+        <v>20.07525094250959</v>
       </c>
       <c r="O7" t="n">
-        <v>4.452074333092672</v>
+        <v>4.480541367124021</v>
       </c>
       <c r="P7" t="n">
-        <v>313.9940037746168</v>
+        <v>314.0921972923678</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31758,28 +31930,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005543633911176447</v>
+        <v>-0.0009428816220183273</v>
       </c>
       <c r="J8" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="K8" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L8" t="n">
-        <v>9.542726281197567e-05</v>
+        <v>2.770159070353273e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>3.088907162957509</v>
+        <v>3.10542553113939</v>
       </c>
       <c r="N8" t="n">
-        <v>17.98714455048717</v>
+        <v>18.06340490720577</v>
       </c>
       <c r="O8" t="n">
-        <v>4.241125387263052</v>
+        <v>4.250106458337928</v>
       </c>
       <c r="P8" t="n">
-        <v>314.4864813535892</v>
+        <v>314.5548022142518</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31817,7 +31989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I705"/>
+  <dimension ref="A1:I709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64947,6 +65119,194 @@
         </is>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>-43.58037180750811,172.77729216556327</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>-43.581127011596244,172.77605194951823</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>-43.58177296436168,172.77632099997678</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>-43.58250223558472,172.77628381414507</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>-43.583106726226546,172.77675810687248</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>-43.583676220061065,172.77729571481817</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>-43.58417838152493,172.77788970636314</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>-43.58038206350254,172.777165498446</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>-43.58112725077169,172.7760489951418</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>-43.58177146628061,172.7763292942342</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>-43.58249963198245,172.77629238567118</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>-43.58310846662421,172.77675391119922</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>-43.58367901498788,172.77729070250234</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>-43.58417598865763,172.77789373488878</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>-43.58038611004674,172.77711552093228</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>-43.58112712121834,172.776050595429</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>-43.58176983793095,172.7763383097309</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>-43.58249984027066,172.77629169994913</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>-43.58310770798934,172.77675574008248</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>-43.58367720650584,172.77729394576556</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>-43.584173823682306,172.77789737974499</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>-43.58039506020724,172.7770049795115</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>-43.5811276493973,172.77604407118096</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>-43.5817702721576,172.7763359055985</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-43.58249956255305,172.77629261424522</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>-43.583109091382305,172.77675240506005</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>-43.583678686172966,172.77729129218656</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>-43.584173880655364,172.77789728382774</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I709"/>
+  <dimension ref="A1:I713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23833,6 +23833,138 @@
         <v>309.27</v>
       </c>
       <c r="I709" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>398.78</v>
+      </c>
+      <c r="C710" t="n">
+        <v>320</v>
+      </c>
+      <c r="D710" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="E710" t="n">
+        <v>301.7</v>
+      </c>
+      <c r="F710" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="G710" t="n">
+        <v>306.7</v>
+      </c>
+      <c r="H710" t="n">
+        <v>309.42</v>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>396.35</v>
+      </c>
+      <c r="C711" t="n">
+        <v>320.44</v>
+      </c>
+      <c r="D711" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="E711" t="n">
+        <v>302.49</v>
+      </c>
+      <c r="F711" t="n">
+        <v>309.62</v>
+      </c>
+      <c r="G711" t="n">
+        <v>307.95</v>
+      </c>
+      <c r="H711" t="n">
+        <v>310.46</v>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>391.18</v>
+      </c>
+      <c r="C712" t="n">
+        <v>320.25</v>
+      </c>
+      <c r="D712" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="E712" t="n">
+        <v>302.45</v>
+      </c>
+      <c r="F712" t="n">
+        <v>308.99</v>
+      </c>
+      <c r="G712" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="H712" t="n">
+        <v>310.59</v>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>383.43</v>
+      </c>
+      <c r="C713" t="n">
+        <v>320.21</v>
+      </c>
+      <c r="D713" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="E713" t="n">
+        <v>302.46</v>
+      </c>
+      <c r="F713" t="n">
+        <v>309.32</v>
+      </c>
+      <c r="G713" t="n">
+        <v>307.94</v>
+      </c>
+      <c r="H713" t="n">
+        <v>311.43</v>
+      </c>
+      <c r="I713" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23849,7 +23981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31282,6 +31414,46 @@
       </c>
       <c r="B743" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -31450,28 +31622,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.308673728169489</v>
+        <v>1.244421662944473</v>
       </c>
       <c r="J2" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K2" t="n">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03439997537469419</v>
+        <v>0.03140680798256335</v>
       </c>
       <c r="M2" t="n">
-        <v>44.56350699502457</v>
+        <v>44.65247405555583</v>
       </c>
       <c r="N2" t="n">
-        <v>2680.861501004395</v>
+        <v>2683.442415507511</v>
       </c>
       <c r="O2" t="n">
-        <v>51.7770364254695</v>
+        <v>51.80195378079393</v>
       </c>
       <c r="P2" t="n">
-        <v>413.3967981320494</v>
+        <v>414.0801137258795</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31532,28 +31704,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0005133666112925664</v>
+        <v>-0.003070651138207137</v>
       </c>
       <c r="J3" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K3" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L3" t="n">
-        <v>1.491614437743038e-06</v>
+        <v>5.391345181393614e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.371216937940384</v>
+        <v>2.371924294620267</v>
       </c>
       <c r="N3" t="n">
-        <v>9.944643046290736</v>
+        <v>9.91700157614336</v>
       </c>
       <c r="O3" t="n">
-        <v>3.153512810548062</v>
+        <v>3.14912711336703</v>
       </c>
       <c r="P3" t="n">
-        <v>322.4976514834296</v>
+        <v>322.5246660631989</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31614,28 +31786,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2715234237406272</v>
+        <v>0.2707847135349536</v>
       </c>
       <c r="J4" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K4" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2989510713889451</v>
+        <v>0.3005048733217025</v>
       </c>
       <c r="M4" t="n">
-        <v>2.195921261900983</v>
+        <v>2.187268303954779</v>
       </c>
       <c r="N4" t="n">
-        <v>9.730922299648537</v>
+        <v>9.678798314588891</v>
       </c>
       <c r="O4" t="n">
-        <v>3.119442626439624</v>
+        <v>3.11107671306718</v>
       </c>
       <c r="P4" t="n">
-        <v>328.921690563431</v>
+        <v>328.9294942894129</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31696,28 +31868,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.003105192054354811</v>
+        <v>-0.008316059425706287</v>
       </c>
       <c r="J5" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K5" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L5" t="n">
-        <v>2.925873094261622e-05</v>
+        <v>0.0002112406615287776</v>
       </c>
       <c r="M5" t="n">
-        <v>3.240170652612703</v>
+        <v>3.246964073443011</v>
       </c>
       <c r="N5" t="n">
-        <v>18.54812127068985</v>
+        <v>18.56119263319943</v>
       </c>
       <c r="O5" t="n">
-        <v>4.306752984638178</v>
+        <v>4.30827025999988</v>
       </c>
       <c r="P5" t="n">
-        <v>306.9570650473874</v>
+        <v>307.0121100090554</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31774,28 +31946,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02593271452586272</v>
+        <v>0.01865075218038375</v>
       </c>
       <c r="J6" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K6" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001636293094809615</v>
+        <v>0.0008497635821707039</v>
       </c>
       <c r="M6" t="n">
-        <v>3.49149865225806</v>
+        <v>3.506889702565002</v>
       </c>
       <c r="N6" t="n">
-        <v>23.0948333298483</v>
+        <v>23.19345044672989</v>
       </c>
       <c r="O6" t="n">
-        <v>4.80570841082231</v>
+        <v>4.815957895032918</v>
       </c>
       <c r="P6" t="n">
-        <v>314.9062360902557</v>
+        <v>314.9831609664828</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31852,28 +32024,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01943816097238156</v>
+        <v>0.01141562965642206</v>
       </c>
       <c r="J7" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K7" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001058231597975023</v>
+        <v>0.0003649738931980062</v>
       </c>
       <c r="M7" t="n">
-        <v>3.231817356465426</v>
+        <v>3.254454109610983</v>
       </c>
       <c r="N7" t="n">
-        <v>20.07525094250959</v>
+        <v>20.24041374008377</v>
       </c>
       <c r="O7" t="n">
-        <v>4.480541367124021</v>
+        <v>4.498934733921328</v>
       </c>
       <c r="P7" t="n">
-        <v>314.0921972923678</v>
+        <v>314.1769433776585</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31930,28 +32102,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0009428816220183273</v>
+        <v>-0.005532796609125575</v>
       </c>
       <c r="J8" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="K8" t="n">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L8" t="n">
-        <v>2.770159070353273e-06</v>
+        <v>9.613517828976903e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.10542553113939</v>
+        <v>3.112643912630504</v>
       </c>
       <c r="N8" t="n">
-        <v>18.06340490720577</v>
+        <v>18.05532460865541</v>
       </c>
       <c r="O8" t="n">
-        <v>4.250106458337928</v>
+        <v>4.249155752459</v>
       </c>
       <c r="P8" t="n">
-        <v>314.5548022142518</v>
+        <v>314.6032836960695</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31989,7 +32161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I709"/>
+  <dimension ref="A1:I713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65307,6 +65479,194 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-43.58040264483634,172.77691130240243</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-43.581127759019296,172.7760427170917</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-43.5817702721576,172.7763359055985</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-43.58250081228222,172.7762884999128</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-43.58310677085213,172.77675799929114</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-43.583677480518276,172.77729345436205</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>-43.58417302605981,172.77789872258668</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-43.58040506671881,172.7768813897333</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-43.58112732053119,172.77604813344863</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-43.58176927343623,172.77634143510298</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-43.582498069820794,172.77629752858653</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-43.5831030223028,172.77676703612505</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-43.58367063020675,172.77730573944848</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>-43.58416710086352,172.77790869798108</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-43.58041021942213,172.7768177483676</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-43.581127509878364,172.77604579456724</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-43.58176940370426,172.77634071386328</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-43.5824982086796,172.7762970714385</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-43.58310583371487,172.7767602584997</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-43.58367282230659,172.77730180822113</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>-43.58416636021392,172.77790994490525</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-43.58041794342742,172.77672234784768</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-43.58112754974091,172.77604530217116</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-43.58176996819895,172.7763375884912</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-43.58249817396489,172.77629718572553</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-43.583104361070504,172.77676380868448</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-43.583670685009245,172.7773056411678</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>-43.58416157447773,172.77791800195297</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0440/nzd0440.xlsx
+++ b/data/nzd0440/nzd0440.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I713"/>
+  <dimension ref="A1:I716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23965,6 +23965,105 @@
         <v>311.43</v>
       </c>
       <c r="I713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>388.23</v>
+      </c>
+      <c r="C714" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="D714" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="E714" t="n">
+        <v>302.6</v>
+      </c>
+      <c r="F714" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="G714" t="n">
+        <v>307.86</v>
+      </c>
+      <c r="H714" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="C715" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="D715" t="n">
+        <v>336</v>
+      </c>
+      <c r="E715" t="n">
+        <v>302.69</v>
+      </c>
+      <c r="F715" t="n">
+        <v>308.98</v>
+      </c>
+      <c r="G715" t="n">
+        <v>307.73</v>
+      </c>
+      <c r="H715" t="n">
+        <v>311.76</v>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>383.71</v>
+      </c>
+      <c r="C716" t="n">
+        <v>321.19</v>
+      </c>
+      <c r="D716" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="E716" t="n">
+        <v>303.07</v>
+      </c>
+      <c r="F716" t="n">
+        <v>309.44</v>
+      </c>
+      <c r="G716" t="n">
+        <v>308.13</v>
+      </c>
+      <c r="H716" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="I716" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23981,7 +24080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B747"/>
+  <dimension ref="A1:B750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31454,6 +31553,36 @@
       </c>
       <c r="B747" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -31622,28 +31751,28 @@
         <v>0.1528</v>
       </c>
       <c r="I2" t="n">
-        <v>1.244421662944473</v>
+        <v>1.189312680352806</v>
       </c>
       <c r="J2" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K2" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03140680798256335</v>
+        <v>0.02885654648371483</v>
       </c>
       <c r="M2" t="n">
-        <v>44.65247405555583</v>
+        <v>44.75585729670033</v>
       </c>
       <c r="N2" t="n">
-        <v>2683.442415507511</v>
+        <v>2689.658418782848</v>
       </c>
       <c r="O2" t="n">
-        <v>51.80195378079393</v>
+        <v>51.86191684447122</v>
       </c>
       <c r="P2" t="n">
-        <v>414.0801137258795</v>
+        <v>414.6680267048378</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31704,28 +31833,28 @@
         <v>0.0927</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.003070651138207137</v>
+        <v>-0.004648863603561739</v>
       </c>
       <c r="J3" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K3" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L3" t="n">
-        <v>5.391345181393614e-05</v>
+        <v>0.00012458494150136</v>
       </c>
       <c r="M3" t="n">
-        <v>2.371924294620267</v>
+        <v>2.370691975183217</v>
       </c>
       <c r="N3" t="n">
-        <v>9.91700157614336</v>
+        <v>9.890696571509967</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14912711336703</v>
+        <v>3.144947785180219</v>
       </c>
       <c r="P3" t="n">
-        <v>322.5246660631989</v>
+        <v>322.5413891321633</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31786,28 +31915,28 @@
         <v>0.1346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2707847135349536</v>
+        <v>0.2705010181141983</v>
       </c>
       <c r="J4" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K4" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3005048733217025</v>
+        <v>0.302099483075206</v>
       </c>
       <c r="M4" t="n">
-        <v>2.187268303954779</v>
+        <v>2.179494893014067</v>
       </c>
       <c r="N4" t="n">
-        <v>9.678798314588891</v>
+        <v>9.639051011073315</v>
       </c>
       <c r="O4" t="n">
-        <v>3.11107671306718</v>
+        <v>3.104682111114327</v>
       </c>
       <c r="P4" t="n">
-        <v>328.9294942894129</v>
+        <v>328.9324984345593</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31868,28 +31997,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008316059425706287</v>
+        <v>-0.01168976317074568</v>
       </c>
       <c r="J5" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K5" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002112406615287776</v>
+        <v>0.0004199000389132346</v>
       </c>
       <c r="M5" t="n">
-        <v>3.246964073443011</v>
+        <v>3.249681640088027</v>
       </c>
       <c r="N5" t="n">
-        <v>18.56119263319943</v>
+        <v>18.54966387581408</v>
       </c>
       <c r="O5" t="n">
-        <v>4.30827025999988</v>
+        <v>4.306932072347332</v>
       </c>
       <c r="P5" t="n">
-        <v>307.0121100090554</v>
+        <v>307.0478614346701</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31946,28 +32075,28 @@
         <v>0.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01865075218038375</v>
+        <v>0.01330833227058252</v>
       </c>
       <c r="J6" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K6" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008497635821707039</v>
+        <v>0.0004339703388770433</v>
       </c>
       <c r="M6" t="n">
-        <v>3.506889702565002</v>
+        <v>3.518276548735704</v>
       </c>
       <c r="N6" t="n">
-        <v>23.19345044672989</v>
+        <v>23.26224601603439</v>
       </c>
       <c r="O6" t="n">
-        <v>4.815957895032918</v>
+        <v>4.823095066037408</v>
       </c>
       <c r="P6" t="n">
-        <v>314.9831609664828</v>
+        <v>315.0397761003358</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32024,28 +32153,28 @@
         <v>0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01141562965642206</v>
+        <v>0.005866238673098926</v>
       </c>
       <c r="J7" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K7" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003649738931980062</v>
+        <v>9.649257265309519e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>3.254454109610983</v>
+        <v>3.269576432209684</v>
       </c>
       <c r="N7" t="n">
-        <v>20.24041374008377</v>
+        <v>20.3346450589899</v>
       </c>
       <c r="O7" t="n">
-        <v>4.498934733921328</v>
+        <v>4.509395198803261</v>
       </c>
       <c r="P7" t="n">
-        <v>314.1769433776585</v>
+        <v>314.2357522181151</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32102,28 +32231,28 @@
         <v>0.0461</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.005532796609125575</v>
+        <v>-0.007704448793657023</v>
       </c>
       <c r="J8" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K8" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L8" t="n">
-        <v>9.613517828976903e-05</v>
+        <v>0.0001879363843907411</v>
       </c>
       <c r="M8" t="n">
-        <v>3.112643912630504</v>
+        <v>3.11138576894413</v>
       </c>
       <c r="N8" t="n">
-        <v>18.05532460865541</v>
+        <v>18.00709202023414</v>
       </c>
       <c r="O8" t="n">
-        <v>4.249155752459</v>
+        <v>4.243476407408687</v>
       </c>
       <c r="P8" t="n">
-        <v>314.6032836960695</v>
+        <v>314.6262969560508</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32161,7 +32290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I713"/>
+  <dimension ref="A1:I716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65667,6 +65796,147 @@
         </is>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-43.58041315953677,172.77678143462413</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-43.581127499912725,172.7760459176663</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>-43.58176992477629,172.77633782890445</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>-43.582497687959005,172.77629878574356</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>-43.583105565961354,172.77676090398788</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>-43.583671123429234,172.77730485492236</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>-43.58415958042082,172.7779213590558</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-43.58042448136189,172.77664159590492</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-43.581127499912725,172.7760459176663</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>-43.581768839209474,172.77634383923532</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>-43.58249737552663,172.7762998143266</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>-43.583105878340454,172.77676015091836</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-43.583671835861686,172.77730357727347</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>-43.58415969436693,172.77792116722134</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-43.580417664367964,172.77672579457658</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-43.58112657310768,172.776057365875</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-43.58176829642594,172.7763468444007</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-43.582496056367624,172.77630415723254</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>-43.583103825563434,172.77676509966074</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>-43.583669643761795,172.7773075085007</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>-43.58415775728297,172.77792442840675</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
